--- a/data/trans_camb/P6906-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 13,56</t>
+          <t>-8,17; 15,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 22,88</t>
+          <t>-7,04; 21,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 16,23</t>
+          <t>-9,39; 19,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 37,32</t>
+          <t>-6,77; 37,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 33,78</t>
+          <t>-10,35; 35,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 21,53</t>
+          <t>-15,67; 20,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 16,78</t>
+          <t>-4,74; 16,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 21,68</t>
+          <t>-2,79; 21,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 15,51</t>
+          <t>-4,98; 16,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 138,26</t>
+          <t>-40,39; 179,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 219,08</t>
+          <t>-35,6; 236,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 163,41</t>
+          <t>-51,54; 217,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,58; 431,2</t>
+          <t>-26,68; 507,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 407,05</t>
+          <t>-44,01; 484,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,62; 348,47</t>
+          <t>-49,58; 315,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 157,64</t>
+          <t>-23,97; 157,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 202,12</t>
+          <t>-15,5; 203,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 152,59</t>
+          <t>-26,83; 147,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 16,31</t>
+          <t>-10,13; 14,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 7,48</t>
+          <t>-15,76; 6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 5,56</t>
+          <t>-14,89; 5,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 33,82</t>
+          <t>1,17; 32,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 34,12</t>
+          <t>2,34; 34,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 20,9</t>
+          <t>-4,09; 21,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 16,39</t>
+          <t>-2,36; 16,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 12,98</t>
+          <t>-7,25; 11,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 9,8</t>
+          <t>-6,87; 9,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 97,68</t>
+          <t>-37,68; 78,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,33; 42,38</t>
+          <t>-59,32; 38,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 36,92</t>
+          <t>-57,88; 32,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 411,53</t>
+          <t>3,48; 352,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 404,34</t>
+          <t>3,93; 403,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 243,11</t>
+          <t>-16,08; 236,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 99,06</t>
+          <t>-11,04; 97,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 77,73</t>
+          <t>-28,81; 67,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 60,47</t>
+          <t>-28,15; 65,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 30,54</t>
+          <t>2,32; 29,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 16,32</t>
+          <t>-6,88; 17,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 10,17</t>
+          <t>-15,15; 10,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 9,2</t>
+          <t>-24,83; 7,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 18,55</t>
+          <t>-18,85; 15,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 8,0</t>
+          <t>-33,1; 6,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 18,44</t>
+          <t>-2,74; 18,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 13,96</t>
+          <t>-5,66; 14,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 5,56</t>
+          <t>-17,4; 6,11</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 225,39</t>
+          <t>8,46; 206,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 117,16</t>
+          <t>-26,88; 124,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 77,94</t>
+          <t>-61,83; 69,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 53,23</t>
+          <t>-67,91; 46,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 105,37</t>
+          <t>-49,35; 91,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,73; 32,98</t>
+          <t>-80,46; 27,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 112,38</t>
+          <t>-10,03; 103,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 80,17</t>
+          <t>-20,28; 82,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 30,48</t>
+          <t>-64,36; 31,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 8,17</t>
+          <t>-16,37; 8,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 14,98</t>
+          <t>-13,18; 11,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 5,29</t>
+          <t>-18,73; 5,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 21,16</t>
+          <t>-6,84; 22,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 29,72</t>
+          <t>-1,31; 29,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 18,98</t>
+          <t>-4,81; 19,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 9,89</t>
+          <t>-8,4; 10,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 16,52</t>
+          <t>-3,27; 16,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 8,28</t>
+          <t>-8,38; 8,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 36,76</t>
+          <t>-51,72; 33,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 63,53</t>
+          <t>-37,97; 50,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 21,81</t>
+          <t>-55,0; 22,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 119,26</t>
+          <t>-24,24; 119,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 158,44</t>
+          <t>-5,45; 178,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 107,69</t>
+          <t>-16,95; 113,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 43,64</t>
+          <t>-27,27; 47,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 72,32</t>
+          <t>-10,73; 73,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 37,28</t>
+          <t>-28,16; 37,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 9,55</t>
+          <t>-3,41; 9,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,37</t>
+          <t>-5,53; 6,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 3,0</t>
+          <t>-9,5; 3,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 16,64</t>
+          <t>-1,48; 16,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 19,31</t>
+          <t>2,42; 18,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 10,13</t>
+          <t>-5,74; 10,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,55</t>
+          <t>0,21; 10,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,4</t>
+          <t>-0,13; 10,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,9</t>
+          <t>-5,45; 4,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 45,57</t>
+          <t>-13,63; 47,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 36,23</t>
+          <t>-21,49; 34,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 14,6</t>
+          <t>-38,55; 17,02</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 94,27</t>
+          <t>-6,19; 95,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,84; 111,27</t>
+          <t>8,55; 103,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 57,72</t>
+          <t>-21,78; 59,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,85; 51,52</t>
+          <t>0,85; 52,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,12; 50,55</t>
+          <t>-0,47; 51,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 24,0</t>
+          <t>-22,4; 22,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6906-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>5,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 15,19</t>
+          <t>-9,1; 15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 21,77</t>
+          <t>-7,17; 21,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 19,38</t>
+          <t>-8,52; 19,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 37,66</t>
+          <t>-4,37; 36,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 35,79</t>
+          <t>-10,81; 33,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 20,84</t>
+          <t>-13,05; 21,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 16,7</t>
+          <t>-3,74; 16,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 21,37</t>
+          <t>-3,09; 21,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 16,24</t>
+          <t>-5,09; 15,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 179,96</t>
+          <t>-43,73; 168,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 236,92</t>
+          <t>-36,02; 210,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 217,0</t>
+          <t>-45,95; 206,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 507,64</t>
+          <t>-24,04; 515,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 484,65</t>
+          <t>-53,41; 357,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 315,28</t>
+          <t>-49,02; 309,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 157,24</t>
+          <t>-20,95; 160,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 203,35</t>
+          <t>-13,45; 201,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 147,11</t>
+          <t>-26,18; 145,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,29</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,7</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 14,05</t>
+          <t>-10,02; 13,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 6,63</t>
+          <t>-15,31; 7,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 5,92</t>
+          <t>-13,63; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 32,07</t>
+          <t>2,33; 34,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 34,42</t>
+          <t>2,19; 34,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 21,57</t>
+          <t>-3,12; 22,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 16,47</t>
+          <t>-1,41; 17,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 11,75</t>
+          <t>-6,64; 12,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 9,58</t>
+          <t>-6,13; 10,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,73%</t>
+          <t>-13,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 78,83</t>
+          <t>-39,87; 80,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 38,88</t>
+          <t>-59,22; 42,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,88; 32,34</t>
+          <t>-50,69; 42,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 352,1</t>
+          <t>3,67; 411,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 403,24</t>
+          <t>5,36; 377,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 236,45</t>
+          <t>-17,47; 274,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 97,91</t>
+          <t>-8,0; 103,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 67,67</t>
+          <t>-28,01; 75,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 65,48</t>
+          <t>-25,45; 63,05</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 29,86</t>
+          <t>2,8; 30,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 17,88</t>
+          <t>-6,67; 18,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 10,19</t>
+          <t>-15,12; 10,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 7,9</t>
+          <t>-23,61; 10,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 15,67</t>
+          <t>-16,76; 16,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 6,33</t>
+          <t>-16,37; 16,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 18,55</t>
+          <t>-3,79; 18,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 14,38</t>
+          <t>-6,9; 12,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 6,11</t>
+          <t>-9,18; 10,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-17,2%</t>
+          <t>-11,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,73%</t>
+          <t>-1,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-19,43%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 206,55</t>
+          <t>6,36; 207,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 124,82</t>
+          <t>-27,39; 133,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 69,31</t>
+          <t>-60,93; 78,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,91; 46,65</t>
+          <t>-65,79; 68,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 91,13</t>
+          <t>-47,18; 96,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,46; 27,62</t>
+          <t>-45,33; 102,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 103,16</t>
+          <t>-14,49; 102,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 82,4</t>
+          <t>-25,49; 72,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,36; 31,03</t>
+          <t>-34,26; 61,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,49</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>8,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 8,74</t>
+          <t>-15,95; 8,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 11,92</t>
+          <t>-11,84; 12,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 5,03</t>
+          <t>-17,16; 6,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 22,05</t>
+          <t>-7,02; 21,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 29,99</t>
+          <t>-0,14; 30,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 19,01</t>
+          <t>-3,74; 20,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 10,76</t>
+          <t>-8,75; 10,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 16,81</t>
+          <t>-3,54; 15,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 8,39</t>
+          <t>-7,86; 8,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-22,42%</t>
+          <t>-21,07%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,68%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,72; 33,73</t>
+          <t>-47,77; 36,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 50,34</t>
+          <t>-35,31; 51,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 22,85</t>
+          <t>-51,61; 31,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 119,83</t>
+          <t>-25,87; 125,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 178,85</t>
+          <t>-1,07; 177,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 113,31</t>
+          <t>-12,46; 124,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 47,17</t>
+          <t>-28,49; 46,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 73,09</t>
+          <t>-12,27; 68,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 37,93</t>
+          <t>-25,22; 36,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 9,42</t>
+          <t>-2,47; 9,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,93</t>
+          <t>-5,1; 7,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,13</t>
+          <t>-8,54; 3,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 16,53</t>
+          <t>-0,37; 15,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,71</t>
+          <t>3,18; 19,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 10,44</t>
+          <t>-1,44; 12,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,42</t>
+          <t>0,02; 9,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 10,11</t>
+          <t>0,24; 10,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,59</t>
+          <t>-2,86; 6,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-15,97%</t>
+          <t>-10,96%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 47,86</t>
+          <t>-10,88; 48,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 34,02</t>
+          <t>-19,97; 37,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 17,02</t>
+          <t>-34,33; 18,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 95,64</t>
+          <t>-2,94; 89,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,55; 103,49</t>
+          <t>11,75; 106,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 59,24</t>
+          <t>-5,81; 73,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,85; 52,3</t>
+          <t>0,11; 50,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 51,44</t>
+          <t>1,01; 49,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 22,81</t>
+          <t>-11,95; 30,36</t>
         </is>
       </c>
     </row>
